--- a/site/docs/sam-toolkit/audit-and-review-checklist.xlsx
+++ b/site/docs/sam-toolkit/audit-and-review-checklist.xlsx
@@ -181,6 +181,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C5">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 
@@ -539,6 +544,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C4">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 
@@ -750,6 +760,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C9">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 

--- a/site/docs/sam-toolkit/audit-and-review-checklist.xlsx
+++ b/site/docs/sam-toolkit/audit-and-review-checklist.xlsx
@@ -442,6 +442,33 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Q9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Is there acceptable proof of purchase behind the entitlements for the products in scope? (8.4)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
